--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,49 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>CUAPIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>JULIO ALBERTO</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
   </si>
 </sst>
 </file>
@@ -662,16 +635,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,16 +661,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -708,16 +687,19 @@
         <v>21</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>21</v>
       </c>
-      <c r="E4">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -731,16 +713,19 @@
         <v>10</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -796,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -831,7 +816,7 @@
         <v>89.47</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,16 +910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920221</v>
+        <v>23330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -948,16 +933,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920229</v>
+        <v>23330051920228</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -966,75 +951,6 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920245</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920267</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920290</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>ROSALES</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>JESSICA</t>
@@ -878,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,16 +919,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920220</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -933,16 +942,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920228</v>
+        <v>23330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -951,7 +960,30 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -85,6 +88,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
   </si>
   <si>
     <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -887,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,39 +928,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920220</v>
+        <v>23330051920301</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920222</v>
+        <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -960,21 +969,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920228</v>
+        <v>23330051920222</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -983,6 +992,29 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,40 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -799,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -825,16 +798,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -851,16 +824,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -886,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,94 +901,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920301</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920220</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920222</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920228</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>VALERIO</t>
+  </si>
+  <si>
+    <t>JHON STEVE</t>
   </si>
   <si>
     <t>OSCAR ALEXANDER</t>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,24 +910,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920278</v>
+        <v>23330051920238</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920278</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>3</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20241.xlsx
@@ -76,22 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>VERA</t>
+    <t>VALERIO</t>
   </si>
   <si>
     <t>ALCANTARA</t>
   </si>
   <si>
-    <t>VALERIO</t>
+    <t>OSCAR ALEXANDER</t>
   </si>
   <si>
     <t>JHON STEVE</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920238</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -925,15 +925,15 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920278</v>
+        <v>23330051920238</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -948,10 +948,10 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
